--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         <v>56</v>
       </c>
       <c r="T3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         <v>56</v>
       </c>
       <c r="T4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>46101</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>46038</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45021</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>46038</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45604</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>46188</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44643</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45412</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45246</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>46010</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>45987</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45631</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45299</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44740</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>46211</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>46248</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45827</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>44753</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>44505</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44862</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>45743</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45387</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45348</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45447</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>45989</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45996</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45054</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45300</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>45609</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45114</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45589</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45820</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45165</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45632</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45987</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>44939</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>45996</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45996</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45996</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45030</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>45112</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>46188</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>46188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45508</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44958</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>46211</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45055</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>46261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45726</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>46226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45153</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45181</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45623</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45470</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45996</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45996</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45996</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>46244</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44537</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44491</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44509</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44606</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44830</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44522</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44687</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44656</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44656</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44712</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44676</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44522</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44673</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>44886</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44538</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44805</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44534</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44461</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44566</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44643</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>44511</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44621</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>44706</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>44487</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44601</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44764</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44753</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44522</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44839</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44781</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44827</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44655</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44693</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44482</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44616</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44839</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44498</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44483</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44684</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44592</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44638</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44595</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44983</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45369</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45335</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45257</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44941</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>44990</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>44990</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45635</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45635</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45007</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45720</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45609</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44504</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45251</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45542</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45599</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44539</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45191</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45030</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44814</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44902</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>44796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45665</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45239</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45162</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44649</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45224</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45257</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45377</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45235</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45189</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44649</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45700</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44580</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45239</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45623</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>44664</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>44746</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45229</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45027</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45575</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45609</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45257</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45723</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45004</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44602</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45004</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45631</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45013</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44539</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44582</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45434</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45434</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>44942</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45635</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>44811</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45609</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45330</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>44944</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45672</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45331</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45681</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45422</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44895</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45789</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45553</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45216</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45216</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44614</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45247</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45247</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45705</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45397</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45581</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45544</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45390</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45902</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44595</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45162</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>45702</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45258</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45040</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45743</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45597</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45596</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>44609</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>46140</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45888</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45780</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44671</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45098</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45918</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45386</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45748</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45219</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46140</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45334</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45832</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>46142</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45119</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44944</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45331</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45229</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>44990</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45373</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45330</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>46147</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45562</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44734</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>44539</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>46147</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45944</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45131</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45162</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45432</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45013</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45229</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45012</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45952</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>44586</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45952</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>46150</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45030</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45609</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45390</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>44958</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45959</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44807</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45077</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45645</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45818</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45964</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45265</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44987</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45027</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45294</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44861</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45359</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45993</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45530</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45194</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45120</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44750</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>44750</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>44956</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45197</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45980</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44972</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45386</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>46078</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45993</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>46077</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44897</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45986</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45348</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45831</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>44539</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44539</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>44539</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45268</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45992</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>46161</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45992</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45882</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>45616</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>44659</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>45021</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45000</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44895</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45992</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45995</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45995</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45635</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45659</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>46001</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45539</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>44676</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45331</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>46003</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44593</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44980</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>46008</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>44966</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46041</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45042</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45601</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44670</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>46014</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>46014</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>46014</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45292</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>44572</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45229</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45281</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45700</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44956</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>46021</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44676</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>46170</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45077</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>45467</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>46031</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>45348</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45763</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45021</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>46036</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45989</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45609</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>45623</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>46038</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>44951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45210</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>44834</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45050</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45010</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45635</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>44888</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>46055</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45273</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>46059</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44722</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45637</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>44984</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>46177</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>46065</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44998</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45419</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>44593</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>46181</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>46181</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44990</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>46181</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>46070</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>46181</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45593</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44820</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>46074</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>46079</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>46080</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>46079</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45130</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>46188</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45672</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>46090</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44901</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45741</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45400</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45560</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44539</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>44539</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44944</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>46098</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>46183</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>46183</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44993</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45607</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45096</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>44673</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45006</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45170</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44998</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>46097</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45350</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44851</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44951</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>45631</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>44994</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45306</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>45118</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>45504</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>44537</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45111</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45163</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>44596</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45439</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44573</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>46038</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45635</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45635</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>45301</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>44761</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45135</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>44837</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45213</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>44802</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45434</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45370</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45434</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45033</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45246</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45539</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45965</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45948</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45162</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>44839</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>46246</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>46247</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45635</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45162</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>45624</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>45012</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45555</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>46209</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45210</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>46252</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>46252</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>46211</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45002</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45238</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45330</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45109</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45301</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45397</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>44670</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45420</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>44537</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44941</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45621</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>44831</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44545</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46260</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44889</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>44648</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45131</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>44714</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44722</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45328</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>45498</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
         <v>46224</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>45202</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>45636</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>45036</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>46268</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45300</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45532</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46274</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>46278</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45119</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45251</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45789</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>45300</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45524</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45747</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45645</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>45547</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44539</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45490</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>45573</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45686</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45469</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45330</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45531</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45692</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45607</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44792</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>45446</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45404</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45485</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45693</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45580</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45331</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>44539</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45372</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41946,7 +41946,7 @@
         <v>45803</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>45812</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45812</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45258</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>45832</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45839</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45840</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45593</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>45859</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>45510</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>45622</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>45869</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45825</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>44441</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44038</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45134</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45021</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45134</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45083</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>45134</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45386</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45803</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45737</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45989</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>46163</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>46188</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>46101</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45989</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45987</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>46038</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45412</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44643</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45604</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>46010</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>46174</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45987</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45246</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45631</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>46211</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44740</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45299</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>46268</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44505</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44862</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45387</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45447</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45832</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45348</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45989</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>45996</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>45574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>45987</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45996</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>45996</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45996</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45642</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45054</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45470</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45820</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>45030</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>45112</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45055</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>45153</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45165</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>46211</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45632</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>46261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45300</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>46226</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>44939</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45187</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45114</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45508</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45609</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45181</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45623</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45996</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45996</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45996</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>46244</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44536</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44537</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44491</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44509</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44606</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>44522</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44687</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44656</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44656</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44676</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>44522</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44673</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44886</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44538</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44805</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44534</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44566</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44643</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44511</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>44621</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44706</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>44487</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>44601</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44764</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>44753</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44522</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44839</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44781</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44827</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44655</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44693</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44482</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>44616</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44839</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44498</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44483</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>44684</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>44592</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44638</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>44595</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45400</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45723</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45300</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45330</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45224</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44888</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44837</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45216</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45216</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45562</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45265</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44796</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44814</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>44539</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44539</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44539</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44792</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>46014</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45593</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>46014</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>46014</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45404</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>46021</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45439</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45692</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45446</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45607</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45485</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>44539</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45030</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45580</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45693</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45372</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44944</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45331</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45763</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>46031</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45377</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44889</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45581</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>44983</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>46036</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45989</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44537</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>44895</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>46038</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45539</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45621</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45050</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45539</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45077</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>44609</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>45202</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44902</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>46055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>44539</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44673</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>46059</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>45918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45359</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44595</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45803</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>46065</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>46070</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>46074</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>44664</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44942</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>46079</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>44596</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45575</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45553</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>46079</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45560</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45369</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>46080</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45373</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45637</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45210</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46090</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>46098</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45944</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45397</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45000</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45006</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45257</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45952</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45434</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45952</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45623</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>44722</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45720</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45004</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44966</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45624</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45258</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45027</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45964</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45812</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44602</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45972</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45135</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>45131</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>45191</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>45219</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>45127</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>44649</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45980</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45002</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45467</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>44722</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45635</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45986</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45631</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44750</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44750</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45702</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44582</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45635</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45992</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44734</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45992</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45992</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45992</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45789</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45992</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45530</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46140</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45659</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45995</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45995</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>44761</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45700</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45631</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45902</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45888</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44807</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45098</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>45965</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>46003</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45162</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>44820</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>46008</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45948</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45820</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44670</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45681</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45596</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44614</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>46140</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44990</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44990</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45027</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44895</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45258</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45780</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45832</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>46142</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45111</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>45235</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46147</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>46147</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>46150</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45013</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45832</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45096</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>45741</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45030</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44851</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45386</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45993</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>46078</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>44897</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45294</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45993</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45818</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>46077</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>44941</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45645</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45239</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>44539</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45840</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45839</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45257</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>44998</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>46161</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45882</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45831</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>44901</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45118</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45593</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45370</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45229</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>46041</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44951</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45859</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45162</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46170</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45622</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44537</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45162</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45328</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44944</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44994</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>45510</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44944</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45109</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45544</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>46177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45504</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45869</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46181</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>46181</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>46181</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>46181</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45251</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45163</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45386</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>46188</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45010</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>44980</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45130</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45348</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45331</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45609</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>46183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45825</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45162</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45197</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45432</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45616</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45597</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>46038</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45119</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>44649</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46209</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>46252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45601</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45609</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>46211</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45635</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45434</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45705</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>44670</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44676</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45238</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>46260</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45229</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44676</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44659</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45390</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45301</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45189</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>44746</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45306</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45246</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>44648</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45247</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45247</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45397</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46268</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>46224</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45330</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45012</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>44987</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>46274</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45268</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44834</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45273</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>45077</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45007</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46278</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>45330</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44573</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>45636</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45609</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>45555</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>46286</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45131</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45422</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45348</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45004</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44990</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44580</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45331</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45012</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>44593</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45040</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44951</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44593</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>46247</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>44545</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45021</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>45635</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>45257</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>45419</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>44539</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>44956</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45036</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>45607</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>46246</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45609</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44802</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45213</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37716,7 +37716,7 @@
         <v>44572</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45170</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>44714</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>44539</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>44990</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>44972</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45599</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45042</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45033</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45281</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>44839</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>45013</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>45021</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>44956</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45210</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>45120</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>44539</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38962,7 +38962,7 @@
         <v>45635</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>44941</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45672</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45665</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44861</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>45609</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>45350</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45420</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>45162</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>44671</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>44984</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>45635</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45539</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>44811</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44993</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45434</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45623</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45301</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>45390</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45331</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45700</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45292</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>44958</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45334</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45635</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45194</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44586</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44998</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45498</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45635</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45434</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>45229</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>44504</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45609</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45335</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45542</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45748</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45672</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45532</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>45119</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45300</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45251</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45573</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45524</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45469</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45531</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45789</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45490</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45547</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45645</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44539</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45747</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45330</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45686</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>44038</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>44441</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45134</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45021</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45134</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>45083</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45134</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45386</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>45803</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45737</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45989</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>46163</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>46188</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>46101</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45989</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45219</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45987</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>46038</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45840</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45412</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44643</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45604</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>46010</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>46174</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45987</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45246</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45631</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>46211</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44740</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45299</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>46268</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44505</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44862</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45387</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45447</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45832</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45348</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45743</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45989</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>45996</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>45574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>45987</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45996</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>45996</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45996</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45642</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45054</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45470</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45820</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>45030</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>45112</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45055</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>46188</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>46188</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>45153</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45165</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>46211</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45632</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>46261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45300</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>46226</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>44939</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45187</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45114</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45508</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45609</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45181</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45623</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45996</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45996</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45996</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>46244</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44536</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>44537</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44491</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44509</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44606</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>44522</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44687</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44656</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44656</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44676</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>44522</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44673</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44886</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44538</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44805</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44534</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44566</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44643</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44511</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>44621</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44706</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>44487</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>44601</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44764</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>44753</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44522</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44839</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44781</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44827</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44655</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44693</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44482</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>44616</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44839</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44498</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44483</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>44684</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>44592</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44638</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>44595</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45400</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45723</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45300</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45330</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45224</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44888</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44837</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45216</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45216</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45562</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45265</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44796</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44814</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>44539</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44539</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44539</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44792</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>46014</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45593</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>46014</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>46014</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45404</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>46021</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45439</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45692</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45446</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45607</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45485</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>44539</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45030</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45580</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45693</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45372</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44944</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45331</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45763</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>46031</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45377</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>44889</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45581</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>44983</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>46036</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45989</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44537</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>44895</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>46038</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45539</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45621</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45050</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45539</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45077</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>44609</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>45202</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44902</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>46055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>44539</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44673</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>46059</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>45918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45359</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44595</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45803</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>46065</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>46070</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>46074</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>44664</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44942</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>46079</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>44596</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45575</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45553</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>46079</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45560</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45369</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>46080</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45373</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45637</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45210</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46090</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>46098</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45944</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45397</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45000</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45006</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45257</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45952</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45434</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45952</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45623</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>44722</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45720</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45004</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44966</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45624</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45258</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45027</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45964</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45812</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44602</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45972</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45135</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>45131</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>45191</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>45219</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>45127</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>44649</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45980</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45002</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45467</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>44722</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45635</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45986</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45631</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44750</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44750</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45702</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44582</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45635</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45992</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44734</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45992</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45992</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45992</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45789</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45992</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45530</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>46140</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45659</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45995</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45995</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>44761</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45700</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45631</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45902</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45888</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44807</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45098</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>45965</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>46003</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45162</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>44820</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>46008</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45948</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45820</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44670</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45681</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45596</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44614</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>46140</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44990</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44990</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45027</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44895</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45258</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45780</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45832</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>46142</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45111</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>45235</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46147</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>46147</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>46150</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45013</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45832</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45096</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>45741</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45030</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44851</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45386</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45993</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>46078</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>44897</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45294</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45993</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45818</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>46077</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>44941</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45645</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45239</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>44539</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45840</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45839</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45257</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>44998</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>46161</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45882</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45831</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>44901</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45118</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45593</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45370</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45229</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>46041</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44951</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45859</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45162</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46170</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45622</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44537</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45162</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45328</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44944</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44994</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>45510</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44944</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45109</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45544</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>46177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45504</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45869</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46181</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>46181</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>46181</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>46181</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45251</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45163</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45386</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>46188</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45010</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>44980</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45130</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45348</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45331</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45609</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>46183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45825</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45162</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45197</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45432</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45616</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45597</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>46038</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45119</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>44649</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46209</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>46252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45601</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45609</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>46211</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45635</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45434</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45705</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>44670</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44676</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45238</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>46260</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45229</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44676</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44659</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45390</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45301</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45189</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>44746</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45306</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45246</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>44648</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45247</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45247</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45397</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46268</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>46224</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45330</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45012</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>44987</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>46274</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45268</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>44834</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>45273</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>45077</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45007</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46278</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>45330</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>44573</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>45636</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45609</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>45555</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>46286</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45131</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45422</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45348</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45004</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44990</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44580</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45331</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45012</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>44593</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45040</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44951</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44593</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>46247</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>44545</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45021</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>45635</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>45257</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>45419</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>44539</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>44956</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45036</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>45607</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>46246</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45609</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>44802</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45213</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37716,7 +37716,7 @@
         <v>44572</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45170</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>44714</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>44539</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>44990</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>44972</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45599</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45042</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45033</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45281</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>44839</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>45013</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>45021</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>44956</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45210</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>45120</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>44539</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38962,7 +38962,7 @@
         <v>45635</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>44941</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45672</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45665</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44861</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>45609</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>45350</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45420</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>45162</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>44671</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>44984</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>45635</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45539</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>44811</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44993</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45434</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45623</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45301</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>45390</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45331</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45700</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45292</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>44958</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45334</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45635</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45194</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>44586</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44998</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45498</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45635</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45434</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>45229</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>44504</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45609</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45335</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45542</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45748</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45672</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45532</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>45119</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45300</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45251</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45573</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45524</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45469</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45531</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45789</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45490</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45547</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45645</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44539</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45747</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45330</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45686</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>44038</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>44441</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45134</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45021</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45134</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>45083</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45134</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45386</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>45803</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45737</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45989</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>46163</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>46188</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45987</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45412</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>46010</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45604</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44643</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45989</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46010</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45393</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46174</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>45246</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45987</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45631</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45299</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45827</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>44740</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46211</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>46293</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45832</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45387</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46291</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45348</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45447</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45623</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45574</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>45187</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45300</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45609</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45470</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45987</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45996</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45996</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45996</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45114</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44834</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>45642</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45642</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45589</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>45820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45165</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45632</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44939</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45030</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46261</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>46226</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45508</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>46295</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>44958</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45055</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45726</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45153</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45181</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45996</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>44536</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44491</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44830</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44687</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44676</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44522</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44886</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44538</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>44534</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44566</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>44643</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44511</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44487</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>44601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>44764</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>44753</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44522</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44685</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44827</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44655</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44693</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44482</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>44616</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44839</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44498</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>44868</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>44684</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44592</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>44638</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>44595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44983</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45369</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45335</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>44990</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44990</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45635</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45257</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44941</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45720</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45609</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44504</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45635</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45599</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45251</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45542</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45007</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45191</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45251</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45789</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44539</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45300</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45030</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46003</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44814</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45539</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45524</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45747</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44852</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45547</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44539</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>46008</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>44902</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45490</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>44670</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46014</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>46014</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>46014</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45581</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>46021</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>44796</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45665</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45573</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45686</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45469</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45330</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>46031</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45239</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45763</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45162</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>46036</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45989</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>44649</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45224</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>46038</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45257</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45377</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45235</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45692</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45607</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44792</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45446</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>45189</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45404</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45485</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45693</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45580</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45331</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44539</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45372</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45918</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45803</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>46055</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45700</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44580</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>46059</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>44649</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>46065</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>44664</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45373</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>44746</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>46070</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45229</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45575</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45944</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45027</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46074</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>46079</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45609</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45609</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>46080</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>46079</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45952</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45257</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>45723</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45812</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>46090</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45004</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44602</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45631</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45004</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45959</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45013</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44539</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44582</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44942</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>46098</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45434</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45434</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45972</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45635</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44811</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45330</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45609</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44944</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45980</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45672</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45681</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45258</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45986</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>45331</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45422</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44895</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45992</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45553</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45992</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>45992</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45216</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45216</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45995</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45995</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>45247</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45247</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45705</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45832</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45397</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45544</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45390</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45839</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44595</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45948</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45162</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45162</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45840</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45258</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45040</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45597</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45789</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45820</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45593</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44614</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>44609</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44671</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45098</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45386</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45902</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45748</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45702</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45219</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45743</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45596</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45334</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45119</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45859</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44944</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45331</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45229</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44990</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45330</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>46140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45510</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45562</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45888</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>44734</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45780</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>44539</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45622</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45869</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>46140</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45832</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46142</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45131</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45162</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45432</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45013</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45012</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46147</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44586</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>46147</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45609</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45390</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>46150</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45030</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44958</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>44807</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45077</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45645</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45265</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45294</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45993</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44987</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>45027</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45386</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>46078</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45993</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>46077</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>44861</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>45359</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>45831</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>46161</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>45882</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45530</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45194</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45825</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45120</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>44750</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44750</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>44956</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45197</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44972</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44897</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45229</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45348</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>46170</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44539</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44539</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44539</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45268</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45127</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45616</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44659</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>45021</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>46177</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45000</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>44895</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>46181</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46181</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>46181</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>46181</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>45635</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45659</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>46188</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45539</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>44676</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45331</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44593</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>46183</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44980</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>46183</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44966</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45042</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45601</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45292</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>44572</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45281</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45700</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44956</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44676</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>46038</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45077</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45467</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45348</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45021</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>45609</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46209</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45623</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46211</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44951</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45210</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44834</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45050</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45010</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>45635</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>44888</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>46260</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>45273</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44722</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45637</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44648</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>44984</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>44998</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>45419</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>44593</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>46224</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>44990</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>46268</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45593</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44820</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>46274</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>45130</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>46278</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45672</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>44901</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>45741</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>45400</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45560</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>44539</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44539</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44944</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>44993</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45607</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>45096</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44673</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45006</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45170</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>44998</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45350</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>44851</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44951</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>46286</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45631</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44994</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>46246</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>45306</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45118</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>45504</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>44537</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45111</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>45163</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44596</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45439</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>46247</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44573</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45635</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45635</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39735,7 +39735,7 @@
         <v>45301</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44761</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45135</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>44837</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45213</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>44802</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>46097</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45434</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45370</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45434</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45033</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45246</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>46252</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>46252</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45539</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>46294</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>44839</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45635</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45162</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45624</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45012</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>46296</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45555</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45210</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45002</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45238</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45330</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45109</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45301</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45397</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44670</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45420</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>44537</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>44941</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45621</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>44831</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44545</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44889</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45131</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>44714</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44722</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45328</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45498</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45202</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45636</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45036</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45300</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45532</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45119</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>44441</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>44038</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45134</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45021</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45134</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45083</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45134</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45386</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>45803</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>45737</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>45989</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>46163</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>46188</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45987</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45412</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>46010</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45604</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44643</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45989</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46010</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45393</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46174</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>45246</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45987</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45631</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45299</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45827</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>44740</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46211</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>46293</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45832</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45387</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46291</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45348</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45447</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45623</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45574</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>45187</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45300</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45609</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45470</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45987</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45996</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45996</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45996</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45114</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44834</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>45642</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45642</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45589</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>45820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45165</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45632</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44939</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45030</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46261</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>46226</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45508</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>46295</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>44958</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45055</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45726</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45153</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45181</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45996</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>44536</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44491</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44830</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44687</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44676</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44522</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44886</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44538</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>44534</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44566</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>44643</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44511</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44487</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>44601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>44764</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>44753</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44522</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44685</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44827</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44655</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44693</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44482</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>44616</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44839</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44498</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>44868</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>44684</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44592</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>44638</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>44595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44983</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45369</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45335</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>44990</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44990</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45635</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45257</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44941</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45720</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45609</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44504</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45635</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45599</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45251</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45542</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45007</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45191</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45251</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45789</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44539</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45300</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45030</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46003</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44814</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45539</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45524</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45747</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44852</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45547</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44539</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>46008</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>44902</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45490</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>44670</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46014</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>46014</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>46014</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45581</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>46021</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>44796</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45665</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45573</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45686</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45469</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45330</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>46031</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45239</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45763</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45162</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>46036</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45989</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>44649</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45224</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>46038</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45257</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45377</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45235</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45692</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45607</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44792</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45446</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>45189</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45404</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45485</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45693</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45580</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45331</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44539</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45372</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45918</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45803</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>46055</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45700</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44580</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>46059</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>44649</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>46065</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>44664</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45373</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>44746</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>46070</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45229</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45575</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45944</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45027</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46074</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>46079</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45609</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45609</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>46080</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>46079</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45952</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45257</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>45723</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45812</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>46090</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45004</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44602</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45631</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45004</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45959</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45013</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44539</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44582</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>44942</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>46098</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45434</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45434</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45972</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45635</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44811</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45330</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45609</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>44944</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45980</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45672</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45681</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45258</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45986</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>45331</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45422</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44895</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45992</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45553</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45992</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>45992</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45216</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45216</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45995</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45995</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>45247</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45247</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45705</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45832</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45397</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45544</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45390</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45839</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44595</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45948</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45162</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45162</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45840</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45258</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45040</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45597</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45789</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45820</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45593</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44614</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>44609</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44671</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45098</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45386</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45902</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45748</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45702</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45219</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45743</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45596</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45334</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45119</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45859</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44944</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45331</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45229</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44990</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45330</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>46140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45510</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45562</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45888</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>44734</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45780</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>44539</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45622</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45869</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>46140</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45832</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46142</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45131</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45162</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45432</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45013</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45012</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46147</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44586</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>46147</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45609</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45390</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>46150</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45030</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44958</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>44807</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45077</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45645</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45265</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45294</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45993</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44987</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>45027</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45386</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>46078</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45993</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>46077</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>44861</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>45359</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>45831</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>46161</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>45882</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45530</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45194</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45825</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45120</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>44750</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>44750</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>44956</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45197</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44972</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44897</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45229</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45348</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>46170</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44539</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44539</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44539</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45268</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45127</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45616</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44659</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>45021</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32876,7 +32876,7 @@
         <v>46177</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45000</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>44895</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>46181</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>46181</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>46181</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>46181</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>45635</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45659</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>46188</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45539</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>44676</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45331</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44593</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>46183</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44980</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>46183</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44966</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45042</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45601</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45292</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>44572</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45281</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45700</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44956</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44676</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>46038</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45077</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45467</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45348</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45021</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>45609</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46209</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45623</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46211</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44951</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45210</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44834</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45050</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45010</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>45635</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>44888</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>46260</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>45273</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44722</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45637</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44648</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>44984</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>44998</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>45419</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>44593</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>46224</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>44990</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>46268</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45593</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44820</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>46274</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>45130</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>46278</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45672</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>44901</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>45741</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>45400</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45560</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>44539</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44539</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44944</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>44993</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45607</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>45096</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44673</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45006</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45170</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>44998</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45350</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>44851</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44951</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>46286</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45631</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44994</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>46246</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>45306</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45118</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>45504</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>44537</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45111</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>45163</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44596</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45439</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>46247</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44573</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45635</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45635</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39735,7 +39735,7 @@
         <v>45301</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44761</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45135</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>44837</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45213</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>44802</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>46097</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45434</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45370</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45434</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45033</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45246</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>46252</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>46252</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45539</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>46294</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>44839</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45635</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45162</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45624</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45012</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>46296</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45555</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45210</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45002</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45238</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45330</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45109</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45301</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45397</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44670</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45420</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>44537</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>44941</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45621</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>44831</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44545</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44889</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45131</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>44714</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44722</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45328</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45498</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45202</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45636</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45036</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45300</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45532</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45119</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>44441</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>44038</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45134</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45021</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45134</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45083</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45134</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45386</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>45803</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>45737</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>45989</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>46163</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>46188</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45987</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>46038</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45021</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>46038</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45604</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45412</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44643</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>46010</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>46188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45246</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45631</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>46010</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>46174</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45987</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44740</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45299</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46211</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>46293</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45447</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>45743</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>45348</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>46291</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45609</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45609</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45589</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45030</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45726</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45055</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45181</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45153</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45165</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45632</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45470</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45300</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45054</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45987</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45996</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45996</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45996</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44939</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45187</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45114</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45642</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45642</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45508</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>46188</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>46188</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>46211</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>46226</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>46295</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>46261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>46244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44509</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44606</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44830</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44522</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44687</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>44712</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44522</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44673</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44886</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>44538</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44805</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>44534</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44566</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>44685</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44482</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>44616</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44781</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>44487</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44601</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44498</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44655</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44483</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44693</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44764</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44753</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44868</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>44522</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>44839</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>44684</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>44592</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45330</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>44956</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45224</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>45210</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>44638</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44595</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45120</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45013</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45096</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44888</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45216</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45216</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44539</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44837</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45635</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44851</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44941</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44941</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45672</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45665</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44539</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>45350</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45420</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45162</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45562</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44671</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>44796</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45257</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44984</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44998</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45265</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44814</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45400</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45723</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45539</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44811</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>44993</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44901</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45434</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45118</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45300</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45623</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45370</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45301</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45390</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>44539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44539</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>44951</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45331</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45700</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45593</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45292</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>44852</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>44958</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45439</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45581</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>44537</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45162</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45328</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45635</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45194</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>44944</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45030</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>44586</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44998</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45498</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45635</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45377</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44889</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45434</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45229</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44983</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44537</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44895</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45109</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45544</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44504</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45609</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45335</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45542</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45748</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45504</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45672</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45539</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45621</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45050</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45539</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45077</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>44609</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>45119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45300</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45251</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44539</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45163</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45386</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45918</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>44673</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45251</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>45010</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>45359</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44595</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44980</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45130</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45573</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>45524</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>45469</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>45531</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>45348</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45331</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45609</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45789</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45490</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45547</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>45645</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>44539</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45747</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>44664</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44942</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45330</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45686</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44596</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45575</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45553</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45197</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44792</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45560</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45404</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>45369</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45692</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45446</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45607</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45485</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45432</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44539</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>45580</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45693</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45372</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>45616</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45331</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45373</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45637</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45210</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45597</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45119</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>44649</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45803</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45239</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45397</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45000</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45006</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45257</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45601</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45609</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45434</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>45944</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45812</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45812</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45623</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44722</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45720</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>45004</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45635</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45624</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45434</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45258</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45027</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45258</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45705</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44670</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>44676</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45238</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>44602</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45229</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45952</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45135</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45131</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45191</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45959</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45219</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44676</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45127</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45832</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44659</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44649</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45390</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45840</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45002</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45467</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45839</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44722</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45635</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45301</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45972</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>45631</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>44750</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44750</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44582</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45635</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>45593</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45189</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44734</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44746</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45306</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45246</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45247</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45247</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45530</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45659</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>44761</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45700</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45631</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45859</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>45622</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45397</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>44807</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45510</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45098</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>45869</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>44820</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45330</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45012</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44987</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>44831</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45980</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>45825</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45681</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45268</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44834</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45273</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44990</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44990</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45027</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45077</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>44895</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>46098</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45007</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45986</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45330</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44573</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45636</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45609</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45555</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45111</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45992</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45235</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45131</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45992</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45422</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45348</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45992</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45992</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45004</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>44990</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45992</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>44580</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45331</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45995</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45012</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45995</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>46001</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44593</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45040</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44951</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44593</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>46003</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>46008</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>44545</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45702</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45021</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>45635</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>45257</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45419</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44670</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45789</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44539</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>44956</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>46140</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>46014</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>46014</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>46014</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>45036</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>45607</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>46021</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45743</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45609</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45902</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45888</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>44802</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45965</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45763</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45162</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45213</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>44572</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>46031</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45170</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>44714</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45948</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>45820</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>46036</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>44539</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44990</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>44972</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>45989</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>46038</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45596</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44614</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45599</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45042</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>46140</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45033</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>45281</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>44839</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45013</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>45780</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39485,7 +39485,7 @@
         <v>45832</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>46055</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>46059</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>46142</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>46147</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>46147</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>46065</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>46070</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>46150</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>46074</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>46079</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46079</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>46080</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45030</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45386</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45993</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46078</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45294</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45993</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45818</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>46077</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45645</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>46090</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>46161</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45882</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45831</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45229</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>46170</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>46177</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>46181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>46181</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>46181</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46181</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>46188</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>46183</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46183</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>46038</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>46209</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>46211</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44648</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>46268</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>46224</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>46274</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>46278</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>46286</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46247</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>46246</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>46097</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46252</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>46252</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46296</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46301</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>46294</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>46301</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>46301</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>46300</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>46304</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>46260</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44038</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44441</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45021</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45134</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45083</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45134</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45386</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45803</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45737</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45989</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46163</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46188</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45987</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>46038</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45021</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>46038</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45604</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45412</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44643</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>46010</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>46188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45246</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45631</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>46010</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>46174</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45987</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44740</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45299</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>46211</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>46293</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45447</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>45743</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>45348</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>46291</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45609</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45609</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45574</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45589</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45030</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45726</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45055</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45181</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45153</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45165</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45632</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45470</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45300</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45054</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45987</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45996</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45996</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45996</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44939</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45187</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45114</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45642</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45642</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45508</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>46188</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>46188</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>46211</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>46226</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>46295</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>46261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>46244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44509</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44606</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44830</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44522</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44687</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>44712</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44522</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44673</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44886</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>44538</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44805</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>44534</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44566</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>44685</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44482</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>44616</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44781</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>44487</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44601</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44498</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44655</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44483</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44693</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44764</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44753</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44868</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>44522</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>44839</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>44684</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>44592</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45330</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>44956</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45224</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>45210</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>44638</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44595</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45120</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45013</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45096</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44888</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45216</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>45216</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44539</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44837</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45635</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44851</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44941</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44941</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45672</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45665</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44539</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>45350</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45420</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45162</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45562</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44671</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>44796</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45257</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44984</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44998</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45265</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44814</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45400</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45723</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45539</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44811</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>44993</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44901</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45434</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45118</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45300</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45623</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45370</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45301</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45390</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>44539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44539</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>44951</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45331</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45700</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45593</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45292</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>44852</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>44958</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45439</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45581</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>44537</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45162</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45328</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45635</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45194</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>44944</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45030</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>44586</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44998</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45498</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45635</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45377</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44889</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45434</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45229</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44983</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>44537</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44895</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45109</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45544</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44504</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45609</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45335</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45542</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45748</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45504</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45672</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45539</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45621</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45050</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45539</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45077</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>44609</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>45532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>45119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45300</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45251</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44539</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45163</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45386</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45918</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>44673</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45251</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>45010</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>45359</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44595</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44980</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45130</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45573</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>45524</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>45469</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>45531</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>45348</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45331</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45609</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45789</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45490</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45547</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>45645</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>44539</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45747</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>44664</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44942</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45330</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45686</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>44596</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45575</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45553</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45197</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44792</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45560</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45404</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>45369</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45692</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45446</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45607</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45485</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45432</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44539</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>45580</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45693</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45372</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>45616</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45331</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45373</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45637</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45210</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45597</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45119</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>44649</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45803</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45239</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45397</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45000</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45006</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45257</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45601</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45609</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45434</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>45944</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45812</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45812</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45623</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44722</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45720</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>45004</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45635</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45624</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45434</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45258</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45027</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45258</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45705</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>44670</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>44676</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45238</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>44602</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45229</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45952</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45135</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45131</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45191</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45959</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45219</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44676</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45127</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45832</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44659</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44649</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45390</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45840</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45002</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45467</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45839</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44722</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45635</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45301</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45972</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>45631</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>44750</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44750</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44582</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45635</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>45593</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45189</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44734</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44746</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45306</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45246</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45247</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45247</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45530</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45659</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>44761</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45700</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45631</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45859</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>45622</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45397</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>44807</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45510</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45098</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>45869</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>44820</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45330</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45012</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44987</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>44831</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45980</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>45825</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45681</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45268</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44834</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45273</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44990</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44990</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45027</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45077</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>44895</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>46098</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45007</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45986</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45330</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44573</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45636</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45609</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>45555</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45111</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45992</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45235</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45131</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45992</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45422</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45348</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45992</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45992</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45004</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>44990</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45992</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>44580</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45331</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45995</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45012</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45995</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>46001</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44593</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45040</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44951</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44593</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>46003</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>46008</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>44545</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45702</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45021</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>45635</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>45257</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45419</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44670</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45789</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44539</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>44956</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>46140</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>46014</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>46014</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>46014</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>45036</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>45607</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         <v>46021</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>45743</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45609</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45902</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45888</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>44802</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45965</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45763</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45162</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45213</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>44572</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>46031</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45170</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>44714</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45948</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>45820</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>46036</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>44539</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>44990</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>44972</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>45989</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>46038</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45596</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44614</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45599</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>45042</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>46140</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45033</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>45281</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>44839</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45013</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>45780</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39485,7 +39485,7 @@
         <v>45832</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>46055</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>46059</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>46142</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>46147</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>46147</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>46065</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>46070</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>46150</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>46074</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>46079</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46079</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>46080</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>45030</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45386</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45993</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46078</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45294</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45993</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45818</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>46077</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45645</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>46090</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>46161</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45882</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45831</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45229</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>46170</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>46177</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>46181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>46181</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>46181</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46181</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>46188</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>46183</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46183</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>46038</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>46209</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>46211</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44648</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>46268</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>46224</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>46274</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>46278</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>46286</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46247</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>46246</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>46097</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46252</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>46252</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46296</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46301</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>46294</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>46301</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>46301</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>46300</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>46304</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>46260</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44038</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44441</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45021</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45134</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45083</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45134</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45386</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45803</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45737</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45989</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46163</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46188</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
         <v>43</v>
       </c>
       <c r="T5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
         <v>43</v>
       </c>
       <c r="T6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>46038</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45604</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>46188</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44643</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45412</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45989</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46010</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>45246</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45987</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45299</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>44740</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>46211</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>46248</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>46293</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45387</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45348</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>46291</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>45447</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45832</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>45300</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45114</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45820</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>45609</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45987</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45165</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45996</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45996</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45996</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>45632</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44939</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>45112</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>46211</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>46226</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45508</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45055</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>46295</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45726</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>45153</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45181</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>46261</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45470</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>46244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44509</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44606</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44830</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44522</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>44687</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>44712</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44522</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>44673</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44886</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>44538</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44805</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>44534</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44566</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>44621</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>44706</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44487</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>44601</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>44753</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>44764</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44522</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>44839</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>44685</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>44827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>44655</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>44693</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44616</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44839</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44498</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44868</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44684</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44592</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44638</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>44595</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>44983</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45369</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45335</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45257</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>44941</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>44990</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>44990</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>45635</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45635</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45720</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45609</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45007</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44504</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45599</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45251</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45542</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>45539</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44852</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44814</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45665</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44796</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>44649</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45239</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45224</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45162</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45257</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45377</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45030</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45189</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45235</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45623</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44649</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45700</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45239</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44580</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44664</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44746</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45229</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45027</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45609</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45609</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45257</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45004</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45723</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>44602</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45004</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45631</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45013</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44582</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45434</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45434</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>44942</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45635</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>44811</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45330</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45609</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>44944</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45672</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45681</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45789</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45820</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45331</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>44614</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45422</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44895</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45553</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45216</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45216</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45581</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45247</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45247</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45705</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45702</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45397</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45596</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>46140</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45888</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45544</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45780</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45390</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44595</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>46140</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45832</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>46142</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45258</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45040</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45597</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45918</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>46147</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44609</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46147</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44671</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45098</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45386</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>46150</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>45030</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45373</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45748</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45219</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45645</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45818</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45334</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45944</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45119</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44944</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45294</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45331</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45229</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>45993</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44990</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45952</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45952</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45330</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45386</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46078</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45562</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>46077</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>44734</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44539</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45831</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45959</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45964</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>46161</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45882</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45131</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45162</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45972</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45432</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45013</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45012</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44586</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45390</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45980</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44958</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44807</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45077</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45265</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>44987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45027</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45986</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44861</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45359</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45992</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45992</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45992</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45530</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45194</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45995</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>45120</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45995</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>44750</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>44750</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45229</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>46001</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>44956</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45197</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44972</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>46170</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>46003</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>44897</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45348</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44539</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>44539</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44539</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>46008</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45268</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45127</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44670</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>46014</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>46014</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>46014</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45616</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>44659</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45021</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>46021</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45000</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>44895</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>46031</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45635</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45659</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45763</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>46036</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45989</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45539</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>46038</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>44676</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45331</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>46177</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>44593</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>46181</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>46181</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>46181</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44966</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45042</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>46055</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45601</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46059</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45292</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44572</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>46065</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45281</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45700</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>44956</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>44676</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>46070</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45077</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>46074</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45467</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>46079</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>46080</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45348</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>46079</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45021</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>45609</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>46090</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45623</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44951</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>46183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>46183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45210</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>46098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44834</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45050</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45010</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45635</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>44888</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45273</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>44722</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45637</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>44984</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>44998</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>45419</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44593</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44990</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>45593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>44820</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>46038</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45130</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45672</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>44901</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45965</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>45948</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>45741</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45400</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45560</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>44539</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44539</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>44944</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>46209</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>46211</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>44993</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>45607</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45096</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44673</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45006</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>45170</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>44998</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45350</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>44851</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>44951</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>44648</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45631</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>44994</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>46224</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45306</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45118</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45504</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>44537</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45111</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45163</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>44596</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45439</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>46274</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44573</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45635</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45635</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45301</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44761</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45135</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>44837</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45213</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>46278</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>44802</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45434</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45370</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45434</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45033</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45246</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45539</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>44839</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45635</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45162</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45624</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45012</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45555</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45210</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>46286</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45002</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>46246</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>45238</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>45330</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45109</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45301</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45397</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46247</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44670</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45420</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44537</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>44941</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45621</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>44831</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>44545</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>46097</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46252</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46252</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>44889</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>45131</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>44714</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>44722</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45328</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45498</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>46296</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45636</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45036</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45300</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>46301</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>46301</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45532</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>46301</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45119</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45251</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45789</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>46260</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45300</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45524</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45747</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45645</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>45547</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44539</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>45490</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45573</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46300</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45686</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45469</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45330</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45531</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45692</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>46304</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45607</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>44792</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45446</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45404</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45485</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45693</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45580</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45331</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>44539</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45372</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45803</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>46307</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>45812</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45812</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>46268</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45258</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>46294</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45832</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45839</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45840</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45593</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>45859</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45510</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>45622</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45869</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45825</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>44441</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>44038</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45134</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45021</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45134</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45083</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45134</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45386</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45803</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45737</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45989</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>46163</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46188</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>46038</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33069-2025</t>
+          <t>A 4943-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45840</v>
+        <v>44593</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>11.6</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3025,21 +3025,131 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>6</v>
       </c>
       <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Prakttagging
+Gullpudra
+Kandelabersvamp
+Skinntagging
+Svartöra
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 4943-2022 artfynd.xlsx", "A 4943-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 4943-2022 karta.png", "A 4943-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor_geotiff/A 4943-2022 georefererad karta.tif", "A 4943-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 4943-2022 FSC-klagomål.docx", "A 4943-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 4943-2022 FSC-klagomål mail.docx", "A 4943-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 4943-2022 tillsynsbegäran.docx", "A 4943-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 4943-2022 tillsynsbegäran mail.docx", "A 4943-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 33069-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45840</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="n">
         <v>10</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Gröngöling
@@ -3049,116 +3159,116 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 33069-2025 artfynd.xlsx", "A 33069-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 33069-2025 karta.png", "A 33069-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor_geotiff/A 33069-2025 georefererad karta.tif", "A 33069-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 33069-2025 FSC-klagomål.docx", "A 33069-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 33069-2025 FSC-klagomål mail.docx", "A 33069-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 33069-2025 tillsynsbegäran.docx", "A 33069-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 33069-2025 tillsynsbegäran mail.docx", "A 33069-2025")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/fåglar/A 33069-2025 prioriterade fågelarter.docx", "A 33069-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 3006-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>5</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>6</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>6</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Göktyta
@@ -3168,111 +3278,111 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 3006-2026 artfynd.xlsx", "A 3006-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 3006-2026 karta.png", "A 3006-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor_geotiff/A 3006-2026 georefererad karta.tif", "A 3006-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 3006-2026 FSC-klagomål.docx", "A 3006-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 3006-2026 FSC-klagomål mail.docx", "A 3006-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 3006-2026 tillsynsbegäran.docx", "A 3006-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 3006-2026 tillsynsbegäran mail.docx", "A 3006-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/fåglar/A 3006-2026 prioriterade fågelarter.docx", "A 3006-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 15758-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45021</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>2.6</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>6</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>13</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>13</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Orange taggsvamp
@@ -3282,115 +3392,115 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 15758-2023 artfynd.xlsx", "A 15758-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 15758-2023 karta.png", "A 15758-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor_geotiff/A 15758-2023 georefererad karta.tif", "A 15758-2023")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/knärot/A 15758-2023 karta knärot.png", "A 15758-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 15758-2023 FSC-klagomål.docx", "A 15758-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 15758-2023 FSC-klagomål mail.docx", "A 15758-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 15758-2023 tillsynsbegäran.docx", "A 15758-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 15758-2023 tillsynsbegäran mail.docx", "A 15758-2023")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/fåglar/A 15758-2023 prioriterade fågelarter.docx", "A 15758-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 32105-2023</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45119</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>1.3</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>3</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>4</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>6</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>6</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Rödvingetrast
@@ -3400,145 +3510,36 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 32105-2023 artfynd.xlsx", "A 32105-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 32105-2023 karta.png", "A 32105-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor_geotiff/A 32105-2023 georefererad karta.tif", "A 32105-2023")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 32105-2023 FSC-klagomål.docx", "A 32105-2023")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 32105-2023 FSC-klagomål mail.docx", "A 32105-2023")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 32105-2023 tillsynsbegäran.docx", "A 32105-2023")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 32105-2023 tillsynsbegäran mail.docx", "A 32105-2023")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/fåglar/A 32105-2023 prioriterade fågelarter.docx", "A 32105-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 4943-2022</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Prakttagging
-Gullpudra
-Kandelabersvamp
-Skinntagging
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 4943-2022 artfynd.xlsx", "A 4943-2022")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 4943-2022 karta.png", "A 4943-2022")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor_geotiff/A 4943-2022 georefererad karta.tif", "A 4943-2022")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 4943-2022 FSC-klagomål.docx", "A 4943-2022")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 4943-2022 FSC-klagomål mail.docx", "A 4943-2022")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 4943-2022 tillsynsbegäran.docx", "A 4943-2022")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 4943-2022 tillsynsbegäran mail.docx", "A 4943-2022")</f>
         <v/>
       </c>
     </row>
@@ -3562,7 +3563,7 @@
         <v>45604</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3680,7 +3681,7 @@
         <v>46188</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3789,7 +3790,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3907,7 +3908,7 @@
         <v>44643</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4020,7 +4021,7 @@
         <v>45412</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4138,7 +4139,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4256,7 +4257,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4368,7 +4369,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4484,7 +4485,7 @@
         <v>45989</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4597,7 +4598,7 @@
         <v>46010</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4710,7 +4711,7 @@
         <v>45246</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4822,7 +4823,7 @@
         <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4934,7 +4935,7 @@
         <v>45987</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5050,7 +5051,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5168,7 @@
         <v>45989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5281,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5393,7 +5394,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5505,7 +5506,7 @@
         <v>45299</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5621,7 +5622,7 @@
         <v>44740</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5728,7 +5729,7 @@
         <v>46211</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5839,7 +5840,7 @@
         <v>46248</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5946,7 +5947,7 @@
         <v>46293</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6062,7 +6063,7 @@
         <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6169,7 +6170,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6276,7 +6277,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6387,7 +6388,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6493,7 +6494,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6599,7 +6600,7 @@
         <v>45743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6705,7 +6706,7 @@
         <v>45387</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6815,7 +6816,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6925,7 +6926,7 @@
         <v>45348</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7039,7 +7040,7 @@
         <v>46291</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7145,7 +7146,7 @@
         <v>45447</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7255,7 +7256,7 @@
         <v>45832</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7366,7 +7367,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7477,7 +7478,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7587,7 +7588,7 @@
         <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7696,7 +7697,7 @@
         <v>45574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7801,7 +7802,7 @@
         <v>45187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7906,7 +7907,7 @@
         <v>45300</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8011,7 +8012,7 @@
         <v>45609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8121,7 +8122,7 @@
         <v>45642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8226,7 +8227,7 @@
         <v>45114</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8336,7 +8337,7 @@
         <v>45642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8441,7 +8442,7 @@
         <v>44834</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8550,7 +8551,7 @@
         <v>45820</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8655,7 +8656,7 @@
         <v>45589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8760,7 +8761,7 @@
         <v>45609</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8870,7 +8871,7 @@
         <v>45987</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8975,7 +8976,7 @@
         <v>45165</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9080,7 +9081,7 @@
         <v>45996</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9190,7 +9191,7 @@
         <v>45996</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9300,7 +9301,7 @@
         <v>45996</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9414,7 +9415,7 @@
         <v>45632</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9519,7 +9520,7 @@
         <v>44939</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9628,7 +9629,7 @@
         <v>45030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9737,7 +9738,7 @@
         <v>46188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9842,7 +9843,7 @@
         <v>46188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9947,7 +9948,7 @@
         <v>45112</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10056,7 +10057,7 @@
         <v>46211</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10161,7 +10162,7 @@
         <v>46226</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10270,7 +10271,7 @@
         <v>45508</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10375,7 +10376,7 @@
         <v>44958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10480,7 +10481,7 @@
         <v>45055</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10585,7 +10586,7 @@
         <v>46295</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10690,7 +10691,7 @@
         <v>45726</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10795,7 +10796,7 @@
         <v>45153</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10900,7 +10901,7 @@
         <v>45181</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11005,7 +11006,7 @@
         <v>45623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11114,7 +11115,7 @@
         <v>46261</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11224,7 +11225,7 @@
         <v>45470</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11329,7 +11330,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11439,7 +11440,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11549,7 +11550,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11663,7 +11664,7 @@
         <v>46244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11777,7 +11778,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11850,7 +11851,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11923,7 +11924,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11996,7 +11997,7 @@
         <v>44509</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12069,7 +12070,7 @@
         <v>44606</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12142,7 +12143,7 @@
         <v>44830</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12215,7 +12216,7 @@
         <v>44522</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12293,7 +12294,7 @@
         <v>44687</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12366,7 +12367,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12439,7 +12440,7 @@
         <v>44656</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12512,7 +12513,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12585,7 +12586,7 @@
         <v>44712</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12658,7 +12659,7 @@
         <v>44522</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12731,7 +12732,7 @@
         <v>44673</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12804,7 +12805,7 @@
         <v>44886</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12877,7 +12878,7 @@
         <v>44538</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12950,7 +12951,7 @@
         <v>44805</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13023,7 +13024,7 @@
         <v>44534</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13096,7 +13097,7 @@
         <v>44566</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13169,7 +13170,7 @@
         <v>44643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13242,7 +13243,7 @@
         <v>44511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13315,7 +13316,7 @@
         <v>44621</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13388,7 +13389,7 @@
         <v>44706</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13466,7 +13467,7 @@
         <v>44487</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13539,7 +13540,7 @@
         <v>44601</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13612,7 +13613,7 @@
         <v>44753</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13690,7 +13691,7 @@
         <v>44764</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13763,7 +13764,7 @@
         <v>44522</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13836,7 +13837,7 @@
         <v>44839</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13909,7 +13910,7 @@
         <v>44685</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13982,7 +13983,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14055,7 +14056,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14128,7 +14129,7 @@
         <v>44827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14201,7 +14202,7 @@
         <v>44655</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14274,7 +14275,7 @@
         <v>44693</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14347,7 +14348,7 @@
         <v>44616</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14420,7 +14421,7 @@
         <v>44839</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14493,7 +14494,7 @@
         <v>44498</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14566,7 +14567,7 @@
         <v>44868</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14639,7 +14640,7 @@
         <v>44684</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14712,7 +14713,7 @@
         <v>44592</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14785,7 +14786,7 @@
         <v>44638</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14863,7 +14864,7 @@
         <v>44595</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14936,7 +14937,7 @@
         <v>44983</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15009,7 +15010,7 @@
         <v>45369</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15082,7 +15083,7 @@
         <v>45335</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15155,7 +15156,7 @@
         <v>45257</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15228,7 +15229,7 @@
         <v>44941</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15301,7 +15302,7 @@
         <v>44990</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15374,7 +15375,7 @@
         <v>44990</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15447,7 +15448,7 @@
         <v>45635</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15525,7 +15526,7 @@
         <v>45635</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15603,7 +15604,7 @@
         <v>45720</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15676,7 +15677,7 @@
         <v>45609</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15754,7 +15755,7 @@
         <v>45007</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15827,7 +15828,7 @@
         <v>44504</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15900,7 +15901,7 @@
         <v>45599</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15973,7 +15974,7 @@
         <v>45251</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16046,7 +16047,7 @@
         <v>45542</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16119,7 +16120,7 @@
         <v>45191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16192,7 +16193,7 @@
         <v>44539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16265,7 +16266,7 @@
         <v>45539</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16343,7 +16344,7 @@
         <v>44852</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16416,7 +16417,7 @@
         <v>44902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16489,7 +16490,7 @@
         <v>44814</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16562,7 +16563,7 @@
         <v>45665</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16635,7 +16636,7 @@
         <v>44796</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16713,7 +16714,7 @@
         <v>44649</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16786,7 +16787,7 @@
         <v>45239</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16859,7 +16860,7 @@
         <v>45224</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16932,7 +16933,7 @@
         <v>45162</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17005,7 +17006,7 @@
         <v>45257</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17078,7 +17079,7 @@
         <v>45377</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17151,7 +17152,7 @@
         <v>45030</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17224,7 +17225,7 @@
         <v>45189</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17302,7 +17303,7 @@
         <v>45235</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17375,7 +17376,7 @@
         <v>45623</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17448,7 +17449,7 @@
         <v>44649</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17521,7 +17522,7 @@
         <v>45700</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17594,7 +17595,7 @@
         <v>45239</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17672,7 +17673,7 @@
         <v>44580</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17745,7 +17746,7 @@
         <v>44664</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17818,7 +17819,7 @@
         <v>44746</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17891,7 +17892,7 @@
         <v>45229</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17964,7 +17965,7 @@
         <v>45027</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18037,7 +18038,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18110,7 +18111,7 @@
         <v>45609</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18183,7 +18184,7 @@
         <v>45609</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18261,7 +18262,7 @@
         <v>45257</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18334,7 +18335,7 @@
         <v>45004</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18407,7 +18408,7 @@
         <v>45723</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18480,7 +18481,7 @@
         <v>44602</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18553,7 +18554,7 @@
         <v>45004</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18626,7 +18627,7 @@
         <v>45631</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18699,7 +18700,7 @@
         <v>45013</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18772,7 +18773,7 @@
         <v>44539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18845,7 +18846,7 @@
         <v>44582</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18918,7 +18919,7 @@
         <v>45434</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18991,7 +18992,7 @@
         <v>45434</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19064,7 +19065,7 @@
         <v>44942</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19137,7 +19138,7 @@
         <v>45635</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19215,7 +19216,7 @@
         <v>44811</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19288,7 +19289,7 @@
         <v>45330</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19361,7 +19362,7 @@
         <v>45609</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19434,7 +19435,7 @@
         <v>44944</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19507,7 +19508,7 @@
         <v>45672</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19580,7 +19581,7 @@
         <v>45681</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19653,7 +19654,7 @@
         <v>45789</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19726,7 +19727,7 @@
         <v>45820</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19799,7 +19800,7 @@
         <v>45331</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19872,7 +19873,7 @@
         <v>44614</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19945,7 +19946,7 @@
         <v>45422</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20018,7 +20019,7 @@
         <v>44895</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20091,7 +20092,7 @@
         <v>45553</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20164,7 +20165,7 @@
         <v>45216</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20242,7 +20243,7 @@
         <v>45216</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20320,7 +20321,7 @@
         <v>45902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20393,7 +20394,7 @@
         <v>45581</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20471,7 +20472,7 @@
         <v>45247</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20544,7 +20545,7 @@
         <v>45247</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20617,7 +20618,7 @@
         <v>45705</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20690,7 +20691,7 @@
         <v>45702</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20763,7 +20764,7 @@
         <v>45743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20836,7 +20837,7 @@
         <v>45397</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20909,7 +20910,7 @@
         <v>45596</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20987,7 +20988,7 @@
         <v>46140</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21060,7 +21061,7 @@
         <v>45888</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21133,7 +21134,7 @@
         <v>45544</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21206,7 +21207,7 @@
         <v>45780</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21279,7 +21280,7 @@
         <v>45390</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21352,7 +21353,7 @@
         <v>44595</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21425,7 +21426,7 @@
         <v>46140</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21498,7 +21499,7 @@
         <v>45162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21571,7 +21572,7 @@
         <v>45832</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21644,7 +21645,7 @@
         <v>46142</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21717,7 +21718,7 @@
         <v>45258</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21790,7 +21791,7 @@
         <v>45040</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21863,7 +21864,7 @@
         <v>45597</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21936,7 +21937,7 @@
         <v>45918</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22009,7 +22010,7 @@
         <v>46147</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22082,7 +22083,7 @@
         <v>44609</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22155,7 +22156,7 @@
         <v>46147</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22233,7 +22234,7 @@
         <v>44671</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22311,7 +22312,7 @@
         <v>45098</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22384,7 +22385,7 @@
         <v>45386</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22457,7 +22458,7 @@
         <v>46150</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22530,7 +22531,7 @@
         <v>45030</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22603,7 +22604,7 @@
         <v>45373</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22676,7 +22677,7 @@
         <v>45748</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22749,7 +22750,7 @@
         <v>45219</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22822,7 +22823,7 @@
         <v>45645</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22895,7 +22896,7 @@
         <v>45818</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22968,7 +22969,7 @@
         <v>45334</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23041,7 +23042,7 @@
         <v>45944</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23114,7 +23115,7 @@
         <v>45119</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23187,7 +23188,7 @@
         <v>44944</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23260,7 +23261,7 @@
         <v>45294</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23333,7 +23334,7 @@
         <v>45331</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23406,7 +23407,7 @@
         <v>45229</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23479,7 +23480,7 @@
         <v>45993</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23552,7 +23553,7 @@
         <v>44990</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23625,7 +23626,7 @@
         <v>45952</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23698,7 +23699,7 @@
         <v>45952</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23771,7 +23772,7 @@
         <v>45330</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23844,7 +23845,7 @@
         <v>45386</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23917,7 +23918,7 @@
         <v>46078</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23990,7 +23991,7 @@
         <v>45562</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24063,7 +24064,7 @@
         <v>45993</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24136,7 +24137,7 @@
         <v>46077</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24209,7 +24210,7 @@
         <v>44734</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24282,7 +24283,7 @@
         <v>44539</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24355,7 +24356,7 @@
         <v>45831</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24428,7 +24429,7 @@
         <v>45959</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24501,7 +24502,7 @@
         <v>45964</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24574,7 +24575,7 @@
         <v>46161</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24647,7 +24648,7 @@
         <v>45882</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24720,7 +24721,7 @@
         <v>45131</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24793,7 +24794,7 @@
         <v>45162</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24866,7 +24867,7 @@
         <v>45972</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24939,7 +24940,7 @@
         <v>45432</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25012,7 +25013,7 @@
         <v>45013</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25085,7 +25086,7 @@
         <v>45012</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25158,7 +25159,7 @@
         <v>44586</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25231,7 +25232,7 @@
         <v>45390</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25304,7 +25305,7 @@
         <v>45980</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25377,7 +25378,7 @@
         <v>44958</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25450,7 +25451,7 @@
         <v>44807</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25528,7 +25529,7 @@
         <v>45077</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25601,7 +25602,7 @@
         <v>45265</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25674,7 +25675,7 @@
         <v>44987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25747,7 +25748,7 @@
         <v>45027</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25820,7 +25821,7 @@
         <v>45986</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25893,7 +25894,7 @@
         <v>44861</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25966,7 +25967,7 @@
         <v>45359</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26039,7 +26040,7 @@
         <v>45992</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26112,7 +26113,7 @@
         <v>45992</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26185,7 +26186,7 @@
         <v>45992</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26258,7 +26259,7 @@
         <v>45530</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26331,7 +26332,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26404,7 +26405,7 @@
         <v>45992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26477,7 +26478,7 @@
         <v>45194</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26550,7 +26551,7 @@
         <v>45995</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26623,7 +26624,7 @@
         <v>45120</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26696,7 +26697,7 @@
         <v>45995</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26769,7 +26770,7 @@
         <v>44750</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26842,7 +26843,7 @@
         <v>44750</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26915,7 +26916,7 @@
         <v>45229</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26988,7 +26989,7 @@
         <v>46001</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27061,7 +27062,7 @@
         <v>44956</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27134,7 +27135,7 @@
         <v>45197</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27207,7 +27208,7 @@
         <v>44972</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27280,7 +27281,7 @@
         <v>46170</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27353,7 +27354,7 @@
         <v>46003</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27426,7 +27427,7 @@
         <v>44897</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27499,7 +27500,7 @@
         <v>45348</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27572,7 +27573,7 @@
         <v>44539</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27645,7 +27646,7 @@
         <v>44539</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27718,7 +27719,7 @@
         <v>44539</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27791,7 +27792,7 @@
         <v>46008</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27864,7 +27865,7 @@
         <v>45268</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27942,7 +27943,7 @@
         <v>45127</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28020,7 +28021,7 @@
         <v>44670</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28093,7 +28094,7 @@
         <v>46014</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28171,7 +28172,7 @@
         <v>46014</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28249,7 +28250,7 @@
         <v>46014</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28327,7 +28328,7 @@
         <v>45616</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28400,7 +28401,7 @@
         <v>44659</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28473,7 +28474,7 @@
         <v>45021</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28546,7 +28547,7 @@
         <v>46021</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28619,7 +28620,7 @@
         <v>45000</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28697,7 +28698,7 @@
         <v>44895</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28770,7 +28771,7 @@
         <v>46031</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28843,7 +28844,7 @@
         <v>45635</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28921,7 +28922,7 @@
         <v>45659</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28994,7 +28995,7 @@
         <v>45763</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29067,7 +29068,7 @@
         <v>46036</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29140,7 +29141,7 @@
         <v>45989</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29218,7 +29219,7 @@
         <v>45539</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29291,7 +29292,7 @@
         <v>46038</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29369,7 +29370,7 @@
         <v>44676</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29442,7 +29443,7 @@
         <v>45331</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29515,7 +29516,7 @@
         <v>46177</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29593,7 +29594,7 @@
         <v>44593</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29666,7 +29667,7 @@
         <v>44980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29739,7 +29740,7 @@
         <v>46181</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29812,7 +29813,7 @@
         <v>46181</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29885,7 +29886,7 @@
         <v>46181</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29958,7 +29959,7 @@
         <v>46181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30031,7 +30032,7 @@
         <v>44966</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30104,7 +30105,7 @@
         <v>45042</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30177,7 +30178,7 @@
         <v>46055</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30250,7 +30251,7 @@
         <v>45601</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30323,7 +30324,7 @@
         <v>46059</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30396,7 +30397,7 @@
         <v>45292</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30469,7 +30470,7 @@
         <v>44572</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30542,7 +30543,7 @@
         <v>46065</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30615,7 +30616,7 @@
         <v>45281</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30688,7 +30689,7 @@
         <v>45700</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30761,7 +30762,7 @@
         <v>44956</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30834,7 +30835,7 @@
         <v>44676</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30907,7 +30908,7 @@
         <v>46188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30980,7 +30981,7 @@
         <v>46070</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31058,7 +31059,7 @@
         <v>45077</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31131,7 +31132,7 @@
         <v>46074</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31204,7 +31205,7 @@
         <v>45467</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31277,7 +31278,7 @@
         <v>46079</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31350,7 +31351,7 @@
         <v>46080</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31423,7 +31424,7 @@
         <v>45348</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31496,7 +31497,7 @@
         <v>46079</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31569,7 +31570,7 @@
         <v>45021</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31647,7 +31648,7 @@
         <v>45609</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31725,7 +31726,7 @@
         <v>46090</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31798,7 +31799,7 @@
         <v>45623</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31871,7 +31872,7 @@
         <v>44951</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31944,7 +31945,7 @@
         <v>46183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32017,7 +32018,7 @@
         <v>46183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32090,7 +32091,7 @@
         <v>45210</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32168,7 +32169,7 @@
         <v>46098</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32241,7 +32242,7 @@
         <v>44834</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32314,7 +32315,7 @@
         <v>45050</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32387,7 +32388,7 @@
         <v>45010</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32460,7 +32461,7 @@
         <v>45635</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32538,7 +32539,7 @@
         <v>44888</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32611,7 +32612,7 @@
         <v>45273</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32684,7 +32685,7 @@
         <v>44722</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32757,7 +32758,7 @@
         <v>45637</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32830,7 +32831,7 @@
         <v>44984</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32903,7 +32904,7 @@
         <v>44998</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32976,7 +32977,7 @@
         <v>45419</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33049,7 +33050,7 @@
         <v>44593</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33122,7 +33123,7 @@
         <v>44990</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33195,7 +33196,7 @@
         <v>45593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33268,7 +33269,7 @@
         <v>44820</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33346,7 +33347,7 @@
         <v>46038</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33424,7 +33425,7 @@
         <v>45130</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33497,7 +33498,7 @@
         <v>45672</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33570,7 +33571,7 @@
         <v>44901</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33643,7 +33644,7 @@
         <v>45965</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33721,7 +33722,7 @@
         <v>45948</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33794,7 +33795,7 @@
         <v>45162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33867,7 +33868,7 @@
         <v>45741</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33940,7 +33941,7 @@
         <v>45400</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34013,7 +34014,7 @@
         <v>45560</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34086,7 +34087,7 @@
         <v>44539</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34159,7 +34160,7 @@
         <v>44539</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34232,7 +34233,7 @@
         <v>44944</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34305,7 +34306,7 @@
         <v>46209</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34378,7 +34379,7 @@
         <v>46211</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34451,7 +34452,7 @@
         <v>44993</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34524,7 +34525,7 @@
         <v>45607</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34597,7 +34598,7 @@
         <v>45096</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34670,7 +34671,7 @@
         <v>44673</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34743,7 +34744,7 @@
         <v>45006</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34816,7 +34817,7 @@
         <v>45170</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34894,7 +34895,7 @@
         <v>44998</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34967,7 +34968,7 @@
         <v>45350</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35040,7 +35041,7 @@
         <v>44851</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35113,7 +35114,7 @@
         <v>44951</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35186,7 +35187,7 @@
         <v>44648</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35259,7 +35260,7 @@
         <v>45631</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35332,7 +35333,7 @@
         <v>44994</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35405,7 +35406,7 @@
         <v>46224</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35478,7 +35479,7 @@
         <v>45306</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35551,7 +35552,7 @@
         <v>45118</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35624,7 +35625,7 @@
         <v>45504</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35697,7 +35698,7 @@
         <v>44537</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35770,7 +35771,7 @@
         <v>45111</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35848,7 +35849,7 @@
         <v>45163</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35921,7 +35922,7 @@
         <v>44596</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35994,7 +35995,7 @@
         <v>45439</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36072,7 +36073,7 @@
         <v>46274</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36145,7 +36146,7 @@
         <v>44573</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36218,7 +36219,7 @@
         <v>45635</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36296,7 +36297,7 @@
         <v>45635</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36374,7 +36375,7 @@
         <v>45301</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36447,7 +36448,7 @@
         <v>44761</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36525,7 +36526,7 @@
         <v>45135</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36603,7 +36604,7 @@
         <v>44837</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36676,7 +36677,7 @@
         <v>45213</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36749,7 +36750,7 @@
         <v>46278</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36822,7 +36823,7 @@
         <v>44802</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36895,7 +36896,7 @@
         <v>45434</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36968,7 +36969,7 @@
         <v>45370</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37041,7 +37042,7 @@
         <v>45434</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37114,7 +37115,7 @@
         <v>45033</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37187,7 +37188,7 @@
         <v>45246</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37260,7 +37261,7 @@
         <v>45539</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37338,7 +37339,7 @@
         <v>44839</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37411,7 +37412,7 @@
         <v>45635</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37489,7 +37490,7 @@
         <v>45162</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37562,7 +37563,7 @@
         <v>45624</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37635,7 +37636,7 @@
         <v>45012</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37708,7 +37709,7 @@
         <v>45555</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37781,7 +37782,7 @@
         <v>45210</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37854,7 +37855,7 @@
         <v>46286</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37927,7 +37928,7 @@
         <v>45002</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38000,7 +38001,7 @@
         <v>46246</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38073,7 +38074,7 @@
         <v>45238</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38146,7 +38147,7 @@
         <v>45330</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38219,7 +38220,7 @@
         <v>45109</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38292,7 +38293,7 @@
         <v>45301</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38365,7 +38366,7 @@
         <v>45397</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38438,7 +38439,7 @@
         <v>46247</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38511,7 +38512,7 @@
         <v>44670</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38584,7 +38585,7 @@
         <v>45420</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38657,7 +38658,7 @@
         <v>44537</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38730,7 +38731,7 @@
         <v>44941</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38803,7 +38804,7 @@
         <v>45621</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38876,7 +38877,7 @@
         <v>44831</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38949,7 +38950,7 @@
         <v>44545</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39022,7 +39023,7 @@
         <v>46097</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39100,7 +39101,7 @@
         <v>46252</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39173,7 +39174,7 @@
         <v>46252</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39246,7 +39247,7 @@
         <v>44889</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39324,7 +39325,7 @@
         <v>45131</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39397,7 +39398,7 @@
         <v>44714</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39470,7 +39471,7 @@
         <v>44722</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39548,7 +39549,7 @@
         <v>45328</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39621,7 +39622,7 @@
         <v>45498</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39694,7 +39695,7 @@
         <v>46296</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39767,7 +39768,7 @@
         <v>45202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39840,7 +39841,7 @@
         <v>45636</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39913,7 +39914,7 @@
         <v>45036</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39986,7 +39987,7 @@
         <v>45300</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40059,7 +40060,7 @@
         <v>46301</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40132,7 +40133,7 @@
         <v>46301</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40205,7 +40206,7 @@
         <v>45532</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40278,7 +40279,7 @@
         <v>46301</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40351,7 +40352,7 @@
         <v>45119</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40424,7 +40425,7 @@
         <v>45251</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40502,7 +40503,7 @@
         <v>45789</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40575,7 +40576,7 @@
         <v>46260</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40648,7 +40649,7 @@
         <v>45300</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40721,7 +40722,7 @@
         <v>45524</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40794,7 +40795,7 @@
         <v>45747</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40867,7 +40868,7 @@
         <v>45645</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40940,7 +40941,7 @@
         <v>45547</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41013,7 +41014,7 @@
         <v>44539</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41086,7 +41087,7 @@
         <v>45490</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41159,7 +41160,7 @@
         <v>45573</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41232,7 +41233,7 @@
         <v>46300</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41305,7 +41306,7 @@
         <v>45686</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41378,7 +41379,7 @@
         <v>45469</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41451,7 +41452,7 @@
         <v>45330</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41524,7 +41525,7 @@
         <v>45531</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41597,7 +41598,7 @@
         <v>45692</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41670,7 +41671,7 @@
         <v>46304</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41743,7 +41744,7 @@
         <v>45607</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41816,7 +41817,7 @@
         <v>44792</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41894,7 +41895,7 @@
         <v>45446</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41967,7 +41968,7 @@
         <v>45404</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42040,7 +42041,7 @@
         <v>45485</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42113,7 +42114,7 @@
         <v>45693</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42186,7 +42187,7 @@
         <v>45580</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42259,7 +42260,7 @@
         <v>45331</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42332,7 +42333,7 @@
         <v>44539</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42405,7 +42406,7 @@
         <v>45372</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42478,7 +42479,7 @@
         <v>45803</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42551,7 +42552,7 @@
         <v>46307</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42629,7 +42630,7 @@
         <v>45812</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42702,7 +42703,7 @@
         <v>45812</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42775,7 +42776,7 @@
         <v>46268</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42848,7 +42849,7 @@
         <v>45258</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42921,7 +42922,7 @@
         <v>46294</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42994,7 +42995,7 @@
         <v>45832</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43072,7 +43073,7 @@
         <v>45839</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43145,7 +43146,7 @@
         <v>45840</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43218,7 +43219,7 @@
         <v>45593</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43296,7 +43297,7 @@
         <v>45859</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43369,7 +43370,7 @@
         <v>45510</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43442,7 +43443,7 @@
         <v>45622</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43515,7 +43516,7 @@
         <v>45869</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43593,7 +43594,7 @@
         <v>45825</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43671,7 +43672,7 @@
         <v>44441</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43744,7 +43745,7 @@
         <v>44038</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43817,7 +43818,7 @@
         <v>45134</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43895,7 +43896,7 @@
         <v>45021</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43968,7 +43969,7 @@
         <v>45134</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44046,7 +44047,7 @@
         <v>45083</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44119,7 +44120,7 @@
         <v>45134</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44197,7 +44198,7 @@
         <v>45386</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44270,7 +44271,7 @@
         <v>45803</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44343,7 +44344,7 @@
         <v>45737</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44416,7 +44417,7 @@
         <v>45989</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44494,7 +44495,7 @@
         <v>46163</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44567,7 +44568,7 @@
         <v>46188</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46174</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45219</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45215</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>46038</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44593</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45604</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45412</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44643</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>46010</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45393</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>46010</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45987</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45246</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>46010</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46211</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46248</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>46293</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>46316</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45299</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45348</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>45447</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>45743</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>46291</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45387</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44939</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45187</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45114</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>45508</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45609</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45609</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>46188</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>46188</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45987</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>46211</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45574</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45996</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45996</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45996</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>46226</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45181</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45623</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45470</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>46295</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>46261</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45726</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45642</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>45642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45820</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45054</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45589</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45030</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45112</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44958</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>45055</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45165</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>45632</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>46244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44830</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44687</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44522</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44886</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44538</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44534</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44566</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44643</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>44511</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>44601</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>44764</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>44753</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44522</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44685</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44827</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>44655</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44693</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44839</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>44498</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>44684</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44593</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>44592</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>44638</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44595</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45581</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44545</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>45635</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45400</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45723</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45257</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45419</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>45300</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44539</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44956</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45607</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45330</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45609</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>44802</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>46161</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45882</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45831</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45213</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45224</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44714</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45918</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>44539</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44990</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>44972</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45229</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45599</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>46170</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45033</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45373</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45281</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44839</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>44888</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45013</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45021</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44956</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45216</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45216</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>44837</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46177</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45210</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45944</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45562</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44796</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45120</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45265</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>44814</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>46181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>46181</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>46181</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45635</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44941</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>46181</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45952</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45672</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>45665</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>44861</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45952</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>45350</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45420</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45162</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44671</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>44984</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45959</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45635</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45539</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45964</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>46188</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>44811</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44993</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45434</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>46183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45623</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>46183</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45301</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45390</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45972</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45331</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45700</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44539</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44539</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45292</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>44958</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45334</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45980</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45635</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>45194</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45986</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>46038</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44586</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44998</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>46209</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45498</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45635</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>46211</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45434</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45229</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45992</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45992</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45992</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44504</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45609</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45992</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45335</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45542</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45995</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45748</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45995</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45593</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45672</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>46001</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44648</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46224</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46003</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45532</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>46008</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45300</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44852</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>46278</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>44670</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45251</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>46014</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46014</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>46014</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>46021</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>45573</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>45524</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45469</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45531</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45789</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45490</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>45547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45645</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44539</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45747</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46286</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45763</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45439</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46031</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45330</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45686</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>46036</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45989</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45404</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45692</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>46038</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45446</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45607</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45485</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>44539</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45580</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45693</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45372</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45331</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46247</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45803</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>46055</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>46246</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>46059</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45812</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45812</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>46065</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>46097</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>46070</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>46252</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46074</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>46252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45258</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>46079</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>46296</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>46079</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>46080</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>46090</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45840</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45839</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45030</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>46098</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>44944</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>46301</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45593</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45377</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44889</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45859</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44983</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>46301</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>46301</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45622</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44537</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45510</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>44895</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>46300</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>45869</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46304</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46260</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45825</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45539</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45621</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45050</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45539</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45077</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>44609</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45202</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>44902</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>46307</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45702</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44539</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45789</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44673</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46140</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45743</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45902</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45888</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45359</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44595</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45965</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46268</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45162</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45948</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45820</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>44664</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44942</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45596</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>44614</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44596</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>46140</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45575</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45553</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45560</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45369</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>46316</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>46274</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45780</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45832</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45637</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45210</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>46294</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>46142</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>46147</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>46147</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45239</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45397</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45000</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46150</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45006</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45257</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45434</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45030</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45386</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45623</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45993</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>46078</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45294</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>44722</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45993</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45818</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>46077</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45645</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45720</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45004</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>44966</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45624</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>45258</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45027</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>44602</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45135</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45131</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45191</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45219</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45127</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>44649</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45002</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45467</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>44722</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>45635</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45631</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>44750</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44750</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>44582</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45635</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>44734</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45530</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45659</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>44761</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>45700</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>45631</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>44807</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45098</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>44831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45681</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>44990</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44990</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45027</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>44895</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45111</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45235</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45013</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45096</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45741</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>44851</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>44941</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45239</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>44539</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45257</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>44998</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44901</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45118</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45370</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>44951</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45162</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>44537</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45162</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45328</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44944</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>44994</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>44944</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45109</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45544</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45504</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45251</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45163</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45386</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45010</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>44980</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45130</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45348</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45331</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45609</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45162</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45197</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45432</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>45616</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45597</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45119</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>44649</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>45601</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45609</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45635</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45434</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>45705</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>44670</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44676</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45238</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>45229</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44676</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>44659</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45390</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45301</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>45189</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>44746</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45306</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45246</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45247</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45247</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45397</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45330</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45012</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>44987</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45268</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>44834</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>45273</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45077</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45007</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45330</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>44573</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45636</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45609</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>45555</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45131</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45422</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45348</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45004</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>44990</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>44580</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>45331</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45012</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>44593</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45040</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>44951</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>44038</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>44441</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45134</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>45021</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>45134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45083</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>45134</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45386</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45803</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45737</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45989</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>46163</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>46188</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>46174</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>45219</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45987</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45215</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>46038</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44593</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45604</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45412</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44643</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>46010</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45393</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>46010</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45987</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45246</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>46010</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>46211</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>46248</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>46293</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>46316</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44740</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45299</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45348</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>45447</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>45743</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>46291</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45387</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44939</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45187</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45114</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>45508</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45609</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45609</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>46188</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>46188</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45987</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>46211</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45574</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45996</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45996</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45996</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>46226</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45181</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45623</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45470</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>46295</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>46261</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45726</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45642</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>45642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45820</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45054</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45589</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45030</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45112</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44958</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>45055</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45165</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>45632</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45300</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>46244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44830</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44687</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44522</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44886</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44538</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44534</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44566</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44643</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>44511</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>44601</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>44764</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>44753</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44522</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44685</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44827</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>44655</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44693</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44839</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>44498</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>44684</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44593</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>44592</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>44638</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44595</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45581</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44545</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>45635</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45400</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45723</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45257</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45419</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>45300</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44539</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44956</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45607</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45330</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45609</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>44802</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>46161</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45882</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45831</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45213</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>44572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45224</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44714</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45918</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>44539</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44990</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>44972</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45229</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45599</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>46170</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45033</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45373</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45281</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44839</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>44888</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45013</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45021</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44956</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45216</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45216</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>44837</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46177</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45210</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45944</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45562</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44796</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45120</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45265</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>44814</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>46181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>46181</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>46181</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45635</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44941</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>46181</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45952</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45672</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>45665</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>44861</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45952</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>45350</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45420</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45162</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44671</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>44984</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45959</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45635</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45539</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45964</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>46188</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>44811</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44993</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45434</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>46183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45623</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>46183</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45301</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45390</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45972</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45331</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45700</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44539</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>44539</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45292</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>44958</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45334</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45980</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45635</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>45194</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45986</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>46038</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44586</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44998</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>46209</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45498</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45635</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>46211</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45434</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45229</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45992</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45992</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45992</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44504</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45609</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45992</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45335</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45542</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45995</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45748</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45995</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45593</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45672</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>46001</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44648</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46224</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46003</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45532</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>46008</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45300</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44852</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>46278</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>44670</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45251</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>46014</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>46014</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>46014</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>46021</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>45573</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>45524</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45469</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45531</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45789</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45490</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>45547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45645</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44539</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45747</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46286</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45763</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45439</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46031</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45330</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45686</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>46036</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45989</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45404</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45692</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>46038</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45446</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45607</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45485</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>44539</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45580</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45693</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45372</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45331</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46247</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45803</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>46055</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>46246</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>46059</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45812</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45812</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>46065</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>46097</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>46070</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>46252</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46074</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>46252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45258</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>46079</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>46296</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>46079</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>46080</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45832</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>46090</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45840</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45839</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45030</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>46098</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>44944</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>46301</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45593</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45377</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44889</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45859</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44983</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>46301</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>46301</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45622</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44537</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45510</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>44895</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>46300</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>45869</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46304</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46260</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45825</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45539</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45621</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45050</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45539</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45077</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>44609</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45202</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>44902</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>46307</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45702</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44539</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45789</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44673</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46140</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45743</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45902</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45888</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45359</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44595</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45965</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46268</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45162</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45948</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45820</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>44664</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44942</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45596</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>44614</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44596</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>46140</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45575</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45553</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45560</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45369</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>46316</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>46274</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45780</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45832</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45637</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45210</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>46294</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>46142</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>46147</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>46147</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45239</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45397</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45000</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46150</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45006</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45257</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45434</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45030</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45386</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45623</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45993</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>46078</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45294</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>44722</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45993</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45818</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>46077</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45645</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45720</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45004</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>44966</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45624</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>45258</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45027</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>44602</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45135</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45131</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45191</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45219</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45127</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>44649</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45002</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45467</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>44722</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>45635</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45631</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>44750</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44750</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>44582</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45635</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>44734</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45530</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45659</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>44761</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>45700</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>45631</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>44807</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45098</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>44831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45681</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>44990</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44990</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45027</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>44895</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45111</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45235</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45013</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45096</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45741</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>44851</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>44941</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45239</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>44539</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45257</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>44998</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44901</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45118</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45370</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>44951</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45162</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>44537</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45162</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45328</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>44944</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>44994</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>44944</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45109</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45544</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45504</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45251</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45163</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45386</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45010</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>44980</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45130</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45348</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45331</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45609</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45162</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45197</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45432</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>45616</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45597</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45119</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>44649</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>45601</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45609</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45635</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45434</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>45705</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>44670</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44676</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45238</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>45229</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>44676</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>44659</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45390</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45301</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>45189</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>44746</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45306</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45246</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45247</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45247</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45397</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45330</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45012</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>44987</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45268</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>44834</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>45273</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45077</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45007</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45330</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>44573</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45636</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45609</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>45555</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45131</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45422</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45348</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45004</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>44990</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>44580</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>45331</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45012</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>44593</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45040</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>44951</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>44038</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>44441</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45134</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>45021</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>45134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45083</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>45134</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45386</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45803</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45737</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45989</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>46163</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>46188</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -601,7 +601,7 @@
         <v>44707</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>46010</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46010</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46101</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45989</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>44685</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45989</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>45989</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44753</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45987</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44593</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>45604</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>46010</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>46188</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>44643</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45412</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>46010</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45989</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>46010</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>46174</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45246</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45631</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45987</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>45989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>46010</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>44755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45299</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>45827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44740</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>46211</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>46248</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>46293</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>46316</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>46268</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44862</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45832</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>45743</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45387</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45387</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45348</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45447</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>46291</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45989</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45187</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45470</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45300</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45609</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45114</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>44834</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>45987</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45996</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45996</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45996</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45609</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45165</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45632</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44939</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>45030</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45642</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45112</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>45820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45508</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>46188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44958</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46211</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45055</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>46226</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45726</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45153</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45181</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>45623</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>46295</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>46261</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>46188</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>46244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44537</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44830</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44687</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44676</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44522</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44886</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44538</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44534</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44566</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44643</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>44511</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>44601</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>44764</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>44753</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44522</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44685</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44781</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>44827</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>44655</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44693</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44839</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>44868</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44684</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>44592</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44638</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>44595</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45369</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45335</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>44983</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45257</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44941</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45635</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44990</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44990</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45635</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45720</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45609</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45599</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45007</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>44504</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45251</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45542</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44539</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45191</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44814</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45539</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>44852</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45030</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>44902</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45665</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45239</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45162</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>44649</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45224</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44796</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>45372</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>45189</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45803</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45623</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>45257</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45377</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45235</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>45700</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44580</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>44649</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45239</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>45812</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>45812</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>44664</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45581</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>46031</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45763</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>44746</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45229</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45258</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>46036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45989</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45575</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45027</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>45609</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45609</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45832</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45257</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45723</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45004</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44602</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45839</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45631</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45840</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45004</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45013</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>44539</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44582</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45593</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>44942</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45434</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45434</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45635</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45859</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>44811</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45330</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45510</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45622</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45609</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>44944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45373</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45681</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45825</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45331</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>46055</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45422</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>44895</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45944</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45553</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45216</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45216</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45247</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45247</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>46059</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45705</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45397</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45952</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>46065</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45544</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45390</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45959</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>44595</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>46070</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45162</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45964</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45258</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45040</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45597</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>46074</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>45972</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46079</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>44609</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46080</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46079</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44671</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45098</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45386</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45980</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45748</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>45219</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45986</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>46090</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45334</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45992</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45992</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>45992</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44944</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45995</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45331</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45229</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44990</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45995</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45330</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45562</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44734</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44539</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>46001</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46098</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46003</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>45131</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45162</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45432</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45013</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45012</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>44586</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>46008</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45390</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44670</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>46014</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>46014</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>46014</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>44958</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44807</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>46021</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45077</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45265</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>44987</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45027</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44861</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45359</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45530</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45194</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45120</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44750</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44750</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>44956</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45197</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>44972</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44897</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45348</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44539</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44539</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44539</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45268</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45127</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45616</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>44659</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45948</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45021</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45162</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45000</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44895</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45789</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45820</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45635</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45659</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>44614</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45539</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>44676</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45331</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>44593</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>44980</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45902</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44966</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>45042</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45702</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45743</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>45601</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45596</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45292</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44572</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45281</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45700</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>44956</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>44676</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>46140</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45077</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45888</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45780</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45467</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45348</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45021</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>46140</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45832</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45609</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>46142</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45623</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44951</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>46147</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45210</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>46147</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>44834</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45050</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>46150</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45030</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45010</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45635</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44888</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45645</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45818</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45294</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45993</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>45273</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45386</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44722</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>46078</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45993</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>46077</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45637</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44984</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45831</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>44998</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>46161</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>45419</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44593</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44990</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45882</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>44820</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45130</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>45672</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45229</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>44901</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>46170</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>45741</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>45400</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>45560</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44539</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44539</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>44944</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>44993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45607</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45096</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>44673</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45170</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>44998</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45350</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>46177</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>44851</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44951</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>46181</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>46181</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>46181</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45631</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>44994</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45306</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45118</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45504</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44537</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45111</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>46188</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45163</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>44596</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45439</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>44573</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45635</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45635</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>45301</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>44761</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45135</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>46183</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44837</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45213</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>46183</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>44802</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45434</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45370</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45434</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45033</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>45246</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>45539</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>44839</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45635</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46038</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>45162</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45624</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45012</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45555</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>46209</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45210</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>46211</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45002</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45238</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45330</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45109</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>44648</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45301</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>46224</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45397</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>44670</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45420</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44537</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>44941</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45621</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>44831</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44545</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44889</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45131</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>44714</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44722</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45328</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45498</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39552,7 +39552,7 @@
         <v>46286</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>45202</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>45636</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>45036</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>46246</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45300</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>45532</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>46247</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>45119</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45251</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45789</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45300</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46097</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45524</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45747</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45645</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45547</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>44539</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45490</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>46252</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46252</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45573</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45686</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45469</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45330</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>45531</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45692</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45607</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44792</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45446</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45404</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45485</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45693</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45580</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45331</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>44539</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>46296</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>46301</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>46301</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>46301</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>46260</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>46300</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>46304</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>46307</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         <v>46268</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>46274</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>46316</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>46278</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>46038</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46294</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45952</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45869</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>45992</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>46323</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>46323</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>46323</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>46324</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>46323</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>46323</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>46323</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>44441</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>44038</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45134</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45021</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45134</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45083</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45134</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45386</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44596,7 +44596,7 @@
         <v>45803</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45737</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45989</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44820,7 +44820,7 @@
         <v>46163</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44893,7 +44893,7 @@
         <v>46188</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
